--- a/backend/Ingredients_Nutrition_UPDATED.xlsx
+++ b/backend/Ingredients_Nutrition_UPDATED.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/13387a1e6e41fa80/Desktop/DS440/DS440/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_7BE191B9D320D01BA160DDF0505ED87656CC9452" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CFA7974-F121-4DFA-9E21-DC1254A5C0F0}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="11_7BE191B9D320D01BA160DDF0505ED87656CC9452" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76968FBB-2BC7-4205-AE1D-888F77145A95}"/>
   <bookViews>
-    <workbookView xWindow="1474" yWindow="1474" windowWidth="15197" windowHeight="13757" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="26537" windowHeight="15943" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1465,19 +1478,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P120"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="16.53515625" customWidth="1"/>
-    <col min="2" max="2" width="19.84375" customWidth="1"/>
-    <col min="3" max="3" width="16.3828125" customWidth="1"/>
-    <col min="4" max="4" width="11.15234375" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="15.15234375" customWidth="1"/>
-    <col min="12" max="12" width="15.3828125" customWidth="1"/>
-    <col min="13" max="13" width="15.3046875" customWidth="1"/>
-    <col min="14" max="14" width="19.61328125" customWidth="1"/>
-    <col min="15" max="15" width="15.921875" customWidth="1"/>
-    <col min="16" max="16" width="17.61328125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
@@ -1884,11 +1884,39 @@
       <c r="K11">
         <v>6</v>
       </c>
+      <c r="L11">
+        <f>SUM(L4:L10)</f>
+        <v>291.19999999999993</v>
+      </c>
+      <c r="M11">
+        <f t="shared" ref="M11:P11" si="0">SUM(M4:M10)</f>
+        <v>13.450000000000001</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="0"/>
+        <v>749.83333333333337</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>33.200000000000003</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="0"/>
+        <v>11.366666666666667</v>
+      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>69</v>
       </c>
+      <c r="K12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="K13">
+        <v>6</v>
+      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
@@ -2187,11 +2215,39 @@
       <c r="K21">
         <v>1</v>
       </c>
+      <c r="L21">
+        <f>SUM(L15:L20)</f>
+        <v>332.9</v>
+      </c>
+      <c r="M21">
+        <f t="shared" ref="M21:P21" si="1">SUM(M15:M20)</f>
+        <v>14.2</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="1"/>
+        <v>48.099999999999994</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="1"/>
+        <v>40.4</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="1"/>
+        <v>12.1</v>
+      </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>106</v>
       </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="K23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
@@ -2537,11 +2593,39 @@
       <c r="K32">
         <v>4</v>
       </c>
+      <c r="L32">
+        <f>SUM(L25:L31)</f>
+        <v>648.82500000000005</v>
+      </c>
+      <c r="M32">
+        <f t="shared" ref="M32:P32" si="2">SUM(M25:M31)</f>
+        <v>20.475000000000001</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="2"/>
+        <v>1567.625</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="2"/>
+        <v>85.474999999999994</v>
+      </c>
+      <c r="P32">
+        <f t="shared" si="2"/>
+        <v>30.9</v>
+      </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>147</v>
       </c>
+      <c r="K33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="K34">
+        <v>4</v>
+      </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
@@ -3028,11 +3112,39 @@
       <c r="K46">
         <v>6</v>
       </c>
+      <c r="L46">
+        <f>SUM(L36:L45)</f>
+        <v>625.75</v>
+      </c>
+      <c r="M46">
+        <f t="shared" ref="M46:P46" si="3">SUM(M36:M45)</f>
+        <v>36.1</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="3"/>
+        <v>1382</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="3"/>
+        <v>48.166666666666664</v>
+      </c>
+      <c r="P46">
+        <f t="shared" si="3"/>
+        <v>25.866666666666667</v>
+      </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
         <v>147</v>
       </c>
+      <c r="K47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="K48">
+        <v>6</v>
+      </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
@@ -3425,6 +3537,26 @@
       <c r="K58">
         <v>4</v>
       </c>
+      <c r="L58">
+        <f>SUM(L50:L57)</f>
+        <v>436.5</v>
+      </c>
+      <c r="M58">
+        <f t="shared" ref="M58:P58" si="4">SUM(M50:M57)</f>
+        <v>19</v>
+      </c>
+      <c r="N58">
+        <f t="shared" si="4"/>
+        <v>870.5</v>
+      </c>
+      <c r="O58">
+        <f t="shared" si="4"/>
+        <v>55.7</v>
+      </c>
+      <c r="P58">
+        <f t="shared" si="4"/>
+        <v>15</v>
+      </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
@@ -3689,11 +3821,39 @@
       <c r="K67">
         <v>2</v>
       </c>
+      <c r="L67">
+        <f>SUM(L62:L66)</f>
+        <v>426.75</v>
+      </c>
+      <c r="M67">
+        <f t="shared" ref="M67:P67" si="5">SUM(M62:M66)</f>
+        <v>24.704999999999998</v>
+      </c>
+      <c r="N67">
+        <f t="shared" si="5"/>
+        <v>704.5</v>
+      </c>
+      <c r="O67">
+        <f t="shared" si="5"/>
+        <v>16.850000000000001</v>
+      </c>
+      <c r="P67">
+        <f t="shared" si="5"/>
+        <v>35.049999999999997</v>
+      </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
         <v>280</v>
       </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="K69">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
@@ -4238,18 +4398,46 @@
       <c r="K83">
         <v>4</v>
       </c>
+      <c r="L83">
+        <f>SUM(L71:L82)</f>
+        <v>571.5</v>
+      </c>
+      <c r="M83">
+        <f t="shared" ref="M83:P83" si="6">SUM(M71:M82)</f>
+        <v>26.9</v>
+      </c>
+      <c r="N83">
+        <f t="shared" si="6"/>
+        <v>1354.75</v>
+      </c>
+      <c r="O83">
+        <f t="shared" si="6"/>
+        <v>55.55</v>
+      </c>
+      <c r="P83">
+        <f t="shared" si="6"/>
+        <v>26.95</v>
+      </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
         <v>147</v>
       </c>
+      <c r="K84">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="K85">
+        <v>4</v>
+      </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
         <v>306</v>
       </c>
       <c r="K86">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.4">
@@ -4278,7 +4466,7 @@
         <v>155</v>
       </c>
       <c r="K87">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L87">
         <v>1152</v>
@@ -4322,7 +4510,7 @@
         <v>22</v>
       </c>
       <c r="K88">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L88">
         <v>22.5</v>
@@ -4366,7 +4554,7 @@
         <v>312</v>
       </c>
       <c r="K89">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L89">
         <v>440</v>
@@ -4410,7 +4598,7 @@
         <v>59</v>
       </c>
       <c r="K90">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L90">
         <v>72</v>
@@ -4454,7 +4642,7 @@
         <v>60</v>
       </c>
       <c r="K91">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L91">
         <v>30.5</v>
@@ -4498,7 +4686,7 @@
         <v>47</v>
       </c>
       <c r="K92">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -4542,7 +4730,7 @@
         <v>47</v>
       </c>
       <c r="K93">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L93">
         <v>119</v>
@@ -4565,13 +4753,41 @@
         <v>68</v>
       </c>
       <c r="K94">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="L94">
+        <f>SUM(L87:L93)</f>
+        <v>1836</v>
+      </c>
+      <c r="M94">
+        <f t="shared" ref="M94:P94" si="7">SUM(M87:M93)</f>
+        <v>116.3</v>
+      </c>
+      <c r="N94">
+        <f t="shared" si="7"/>
+        <v>3702.3</v>
+      </c>
+      <c r="O94">
+        <f t="shared" si="7"/>
+        <v>88.9</v>
+      </c>
+      <c r="P94">
+        <f t="shared" si="7"/>
+        <v>101.6</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
         <v>147</v>
       </c>
+      <c r="K95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="K96">
+        <v>1</v>
+      </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
@@ -4896,11 +5112,39 @@
       <c r="K105">
         <v>4</v>
       </c>
+      <c r="L105">
+        <f>SUM(L98:L104)</f>
+        <v>793.25</v>
+      </c>
+      <c r="M105">
+        <f t="shared" ref="M105:P105" si="8">SUM(M98:M104)</f>
+        <v>45.375</v>
+      </c>
+      <c r="N105">
+        <f t="shared" si="8"/>
+        <v>553.5</v>
+      </c>
+      <c r="O105">
+        <f t="shared" si="8"/>
+        <v>68.7</v>
+      </c>
+      <c r="P105">
+        <f t="shared" si="8"/>
+        <v>28.5</v>
+      </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
         <v>147</v>
       </c>
+      <c r="K106">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="K107">
+        <v>4</v>
+      </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
@@ -5367,6 +5611,26 @@
       </c>
       <c r="K120">
         <v>1</v>
+      </c>
+      <c r="L120">
+        <f>SUM(L109:L119)</f>
+        <v>604</v>
+      </c>
+      <c r="M120">
+        <f t="shared" ref="M120:P120" si="9">SUM(M109:M119)</f>
+        <v>33.700000000000003</v>
+      </c>
+      <c r="N120">
+        <f t="shared" si="9"/>
+        <v>3069</v>
+      </c>
+      <c r="O120">
+        <f t="shared" si="9"/>
+        <v>65.099999999999994</v>
+      </c>
+      <c r="P120">
+        <f t="shared" si="9"/>
+        <v>19.099999999999998</v>
       </c>
     </row>
   </sheetData>
